--- a/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
+++ b/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="P13" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/synthesis/new_n512_lanes1/utilization.rpt</t>
+          <t>evidence/baseline/raw_reports/synthesis/new_n512_lanes1/utilization.rpt</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="J7" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="J11" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="J12" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="L2" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M2" s="0" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="L3" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M3" s="0" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M4" s="0" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M5" s="0" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="L6" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M6" s="0" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M7" s="0" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M8" s="0" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/runtime_fft_speed_50MHz.csv</t>
+          <t>evidence/baseline/runtime_fft_speed_50MHz.csv</t>
         </is>
       </c>
       <c r="M9" s="0" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="K3" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="K6" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K7" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="K8" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="K9" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K10" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="K11" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>evidence/baseline/KV260_working_mfcc_fft_bram_tested_20261022/raw_reports/mfcc_integration.json</t>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
         </is>
       </c>
     </row>

--- a/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
+++ b/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
@@ -673,33 +673,49 @@
       <c r="E10" s="2">
         <v>64</v>
       </c>
-      <c r="F10" s="2">
-        <v>647</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.55</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1098</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.47</v>
-      </c>
-      <c r="J10" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1.74</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.08</v>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>OOC post-route; hierarchy inclusive</t>
+          <t>Register/LUT RTL; hardware reimplementation pending</t>
         </is>
       </c>
       <c r="O10" s="3">
@@ -707,7 +723,7 @@
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/utilization_hierarchical_post_route.rpt</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
     </row>
@@ -905,33 +921,49 @@
       <c r="E14" s="2">
         <v>64</v>
       </c>
-      <c r="F14" s="2">
-        <v>30188</v>
-      </c>
-      <c r="G14" s="3">
-        <v>25.78</v>
-      </c>
-      <c r="H14" s="2">
-        <v>41987</v>
-      </c>
-      <c r="I14" s="3">
-        <v>17.92</v>
-      </c>
-      <c r="J14" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>6.25</v>
-      </c>
-      <c r="L14" s="2">
-        <v>19</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1.52</v>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t>OOC post-route; hierarchy inclusive</t>
+          <t>Register/LUT RTL; hardware reimplementation pending</t>
         </is>
       </c>
       <c r="O14" s="3">
@@ -939,7 +971,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/utilization_hierarchical_post_route.rpt</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2466,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2641,8 +2673,30 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>MatrixDCT register/LUT replacement</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Six unit cases; twenty MFCC configurations</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Simulation passes; new physical resource/timing mapping pending</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_20261026/README.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -2916,7 +2970,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2938,149 +2992,161 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>Selection rule</t>
+          <t>MatrixDCT storage replacement</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Keep the latest valid value per test project and configuration. Architecture/pipeline/version names are not separate test projects.</t>
+          <t>Current MatrixDCT uses register/LUT storage. Its new resource and timing fields are pending, not copied from the obsolete BRAM implementation. Latest verified N1024 batch: 43622 cycles. Original hardware reports remain historical evidence.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Configuration key</t>
+          <t>Selection rule</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Project, backend under comparison, N, frequency, output lanes, frame count and stall condition identify a case. Inclusive hierarchy scope is retained.</t>
+          <t>Keep the latest valid value per test project and configuration. Architecture/pipeline/version names are not separate test projects.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Partial updates</t>
+          <t>Configuration key</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Refresh metrics separately: a 150 MHz resource update does not invent new 50/100 MHz resources. Unchanged metrics use the latest available reports. Runtime cycle counts use the latest matching regression and are converted by frequency.</t>
+          <t>Project, backend under comparison, N, frequency, output lanes, frame count and stall condition identify a case. Inclusive hierarchy scope is retained.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Partial updates</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Source paths in tables and JSON are relative to docs/benchmarks/. Per-metric source columns identify the original evidence; different metric groups can come from different packages.</t>
+          <t>Refresh metrics separately: a 150 MHz resource update does not invent new 50/100 MHz resources. Unchanged metrics use the latest available reports. Runtime cycle counts use the latest matching regression and are converted by frequency.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>Resource priority</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>LUT, FF, BRAM and DSP appear first. DCT/C64/SkewDCT8 hierarchy rows are already included in parent totals.</t>
+          <t>Source paths in tables and JSON are relative to docs/benchmarks/. Per-metric source columns identify the original evidence; different metric groups can come from different packages.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>BRAM unit</t>
+          <t>Resource priority</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>One BRAM tile is a 36 Kb equivalent; each RAMB18 counts as 0.5 tile.</t>
+          <t>LUT, FF, BRAM and DSP appear first. DCT/C64/SkewDCT8 hierarchy rows are already included in parent totals.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>FFT evidence</t>
+          <t>BRAM unit</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>XFFT resource reports use fixed-size cores and a 10 ns synthesis clock; custom FFT resources use a shared runtime core after routing at 20 ns. The 64..2048 XFFT latency numbers use runtime_2048. These attributes remain source metadata, not version-specific result rows.</t>
+          <t>One BRAM tile is a 36 Kb equivalent; each RAMB18 counts as 0.5 tile.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>FFT 16-point counting</t>
+          <t>FFT evidence</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Latest reported custom complete-frame latency is 82 cycles; its accompanying regression records 83. The primary table retains the latest reported value and marks this counting discrepancy.</t>
+          <t>XFFT resource reports use fixed-size cores and a 10 ns synthesis clock; custom FFT resources use a shared runtime core after routing at 20 ns. The 64..2048 XFFT latency numbers use runtime_2048. These attributes remain source metadata, not version-specific result rows.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>FFT first output</t>
+          <t>FFT 16-point counting</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>First-output cycles are taken from the latest package reporting that metric (2026-10-22); complete-frame comparisons are updated by the 2026-10-25 package.</t>
+          <t>Latest reported custom complete-frame latency is 82 cycles; its accompanying regression records 83. The primary table retains the latest reported value and marks this counting discrepancy.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>Timing/accuracy scope</t>
+          <t>FFT first output</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>Times are RTL cycles divided by MHz, not board/PS/DMA measurements. Four-frame averages are not independently measured single-frame latency or steady-state II. MFCC reference errors do not isolate DCT error or recognition accuracy.</t>
+          <t>First-output cycles are taken from the latest package reporting that metric (2026-10-22); complete-frame comparisons are updated by the 2026-10-25 package.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Timing/accuracy scope</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Superseded values remain in immutable original reports for traceability, outside primary tables. The explicit paired memory before/after experiment retains both required comparison sides.</t>
+          <t>Times are RTL cycles divided by MHz, not board/PS/DMA measurements. Four-frame averages are not independently measured single-frame latency or steady-state II. MFCC reference errors do not isolate DCT error or recognition accuracy.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Superseded values remain in immutable original reports for traceability, outside primary tables. The explicit paired memory before/after experiment retains both required comparison sides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t>200 MHz status</t>
         </is>
       </c>
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>Not measured for the latest RTL. Frozen-route estimate is approximately -1.409 ns. The old 200 MHz run was interrupted during placement and is not a pass/fail result.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -3481,60 +3547,78 @@
       <c r="F5" s="2">
         <v>50</v>
       </c>
-      <c r="G5" s="2">
-        <v>30188</v>
-      </c>
-      <c r="H5" s="2">
-        <v>41987</v>
-      </c>
-      <c r="I5" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>19</v>
-      </c>
-      <c r="K5" s="3">
-        <v>8.254</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="O5" s="2">
-        <v>0</v>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PENDING_REGISTER_IMPLEMENTATION</t>
         </is>
       </c>
       <c r="Q5" s="2">
-        <v>43687</v>
+        <v>43622</v>
       </c>
       <c r="R5" s="3">
-        <v>873.74</v>
+        <v>872.44</v>
       </c>
       <c r="S5" s="3">
-        <v>218.435</v>
+        <v>218.11</v>
       </c>
       <c r="T5" s="0" t="inlineStr">
         <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/utilization_hierarchical_post_route.rpt</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/timing_post_route.rpt</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5850,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -5781,16 +5865,17 @@
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="65" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="21" width="65" customWidth="1"/>
     <col min="22" max="22" width="65" customWidth="1"/>
+    <col min="23" max="23" width="65" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -5856,50 +5941,55 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Hardware status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Frames</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Batch cycles</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Batch us</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFCC MAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFCC RMSE</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFCC max abs error</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFCC SNR dB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MFCC resource source</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>DCT resource source</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Runtime/precision source</t>
         </is>
@@ -5944,38 +6034,43 @@
       <c r="L2" s="2">
         <v>41</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="N2" s="2">
         <v>4</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>39508</v>
       </c>
-      <c r="O2" s="3">
+      <c r="P2" s="3">
         <v>790.16</v>
       </c>
-      <c r="P2" s="3">
+      <c r="Q2" s="3">
         <v>3.4286065721184498</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="R2" s="3">
         <v>12.49161094141159</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>101.62445254003131</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>16.04862513376996</v>
       </c>
-      <c r="T2" s="0" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>recursive_skewdct_N1024_20261026/raw_reports/skewdct_50MHz/utilization_hierarchical_post_route.rpt</t>
         </is>
       </c>
-      <c r="U2" s="0" t="inlineStr">
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>recursive_skewdct_N1024_20261026/raw_reports/skewdct_50MHz/utilization_hierarchical_post_route.rpt</t>
         </is>
       </c>
-      <c r="V2" s="0" t="inlineStr">
+      <c r="W2" s="0" t="inlineStr">
         <is>
           <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
         </is>
@@ -5996,69 +6091,90 @@
       <c r="D3" s="2">
         <v>50</v>
       </c>
-      <c r="E3" s="2">
-        <v>30188</v>
-      </c>
-      <c r="F3" s="2">
-        <v>41987</v>
-      </c>
-      <c r="G3" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2">
-        <v>647</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1098</v>
-      </c>
-      <c r="K3" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2">
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>PENDING_REGISTER_IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="N3" s="2">
         <v>4</v>
       </c>
-      <c r="N3" s="2">
-        <v>43687</v>
-      </c>
-      <c r="O3" s="3">
-        <v>873.74</v>
+      <c r="O3" s="2">
+        <v>43622</v>
       </c>
       <c r="P3" s="3">
+        <v>872.44</v>
+      </c>
+      <c r="Q3" s="3">
         <v>3.4285470932893625</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>12.490109975036425</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>101.60887915401372</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>16.04966887517948</v>
       </c>
-      <c r="T3" s="0" t="inlineStr">
-        <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/utilization_hierarchical_post_route.rpt</t>
-        </is>
-      </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>recursive_skewdct_N1024_20261026/raw_reports/matrixdct_50MHz/utilization_hierarchical_post_route.rpt</t>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_20261026/verified_results.json</t>
+        </is>
+      </c>
+      <c r="W3" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_20261026/verified_results.json</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V3"/>
+  <autoFilter ref="A1:W3"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>

--- a/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
+++ b/docs/benchmarks/MFCC_Benchmark_Summary.xlsx
@@ -9,12 +9,13 @@
     <sheet name="FFT_Latency" sheetId="5" r:id="rId5"/>
     <sheet name="FFT_Accuracy" sheetId="6" r:id="rId6"/>
     <sheet name="DCT_Comparison" sheetId="7" r:id="rId7"/>
-    <sheet name="Memory_Savings" sheetId="8" r:id="rId8"/>
-    <sheet name="Memory_Regression" sheetId="9" r:id="rId9"/>
-    <sheet name="Timing_Paths" sheetId="10" r:id="rId10"/>
-    <sheet name="Coverage" sheetId="11" r:id="rId11"/>
-    <sheet name="Sources" sheetId="12" r:id="rId12"/>
-    <sheet name="Readme" sheetId="13" r:id="rId13"/>
+    <sheet name="DCT_Standalone" sheetId="8" r:id="rId8"/>
+    <sheet name="Memory_Savings" sheetId="9" r:id="rId9"/>
+    <sheet name="Memory_Regression" sheetId="10" r:id="rId10"/>
+    <sheet name="Timing_Paths" sheetId="11" r:id="rId11"/>
+    <sheet name="Coverage" sheetId="12" r:id="rId12"/>
+    <sheet name="Sources" sheetId="13" r:id="rId13"/>
+    <sheet name="Readme" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -86,7 +87,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -673,49 +674,33 @@
       <c r="E10" s="2">
         <v>64</v>
       </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M10" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F10" s="2">
+        <v>1749</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1.49</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2584</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1.1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.08</v>
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t>Register/LUT RTL; hardware reimplementation pending</t>
+          <t>OOC post-route; user-supplied summary; raw report not supplied</t>
         </is>
       </c>
       <c r="O10" s="3">
@@ -723,7 +708,7 @@
       </c>
       <c r="P10" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -921,49 +906,33 @@
       <c r="E14" s="2">
         <v>64</v>
       </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M14" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="F14" s="2">
+        <v>30110</v>
+      </c>
+      <c r="G14" s="3">
+        <v>25.71</v>
+      </c>
+      <c r="H14" s="2">
+        <v>43473</v>
+      </c>
+      <c r="I14" s="3">
+        <v>18.56</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>4.51</v>
+      </c>
+      <c r="L14" s="2">
+        <v>19</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1.52</v>
       </c>
       <c r="N14" s="0" t="inlineStr">
         <is>
-          <t>Register/LUT RTL; hardware reimplementation pending</t>
+          <t>OOC post-route; user-supplied summary; raw report not supplied</t>
         </is>
       </c>
       <c r="O14" s="3">
@@ -971,7 +940,7 @@
       </c>
       <c r="P14" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -1517,13 +1486,647 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>MatrixDCT</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>Standalone DCT</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="2">
+        <v>50</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" s="2">
+        <v>1847</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1.58</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2717</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>OOC post-route; user-supplied summary; raw report not supplied</t>
+        </is>
+      </c>
+      <c r="O24" s="2">
+        <v>20</v>
+      </c>
+      <c r="P24" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>SkewDCT</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>Standalone DCT</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" s="2">
+        <v>50</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" s="2">
+        <v>5113</v>
+      </c>
+      <c r="G25" s="3">
+        <v>4.37</v>
+      </c>
+      <c r="H25" s="2">
+        <v>12378</v>
+      </c>
+      <c r="I25" s="3">
+        <v>5.28</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>41</v>
+      </c>
+      <c r="M25" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="N25" s="0" t="inlineStr">
+        <is>
+          <t>OOC post-route; user-supplied summary; raw report not supplied</t>
+        </is>
+      </c>
+      <c r="O25" s="2">
+        <v>20</v>
+      </c>
+      <c r="P25" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027/results.json</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P23"/>
+  <autoFilter ref="A1:P25"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FFT N</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Output lanes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Stalls</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Frames</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Before cycles</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>After cycles</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Before batch us at 50MHz</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>After batch us at 50MHz</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cycle change %</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Mismatches to own reference</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1226</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1226</v>
+      </c>
+      <c r="G2" s="3">
+        <v>24.52</v>
+      </c>
+      <c r="H2" s="3">
+        <v>24.52</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1393</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1407</v>
+      </c>
+      <c r="G3" s="3">
+        <v>27.86</v>
+      </c>
+      <c r="H3" s="3">
+        <v>28.14</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.0050251256281406</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2757</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2537</v>
+      </c>
+      <c r="G4" s="3">
+        <v>55.14</v>
+      </c>
+      <c r="H4" s="3">
+        <v>50.74</v>
+      </c>
+      <c r="I4" s="3">
+        <v>-7.979688066739208</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>128</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4304</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4304</v>
+      </c>
+      <c r="G5" s="3">
+        <v>86.08</v>
+      </c>
+      <c r="H5" s="3">
+        <v>86.08</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>256</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6853</v>
+      </c>
+      <c r="F6" s="2">
+        <v>6838</v>
+      </c>
+      <c r="G6" s="3">
+        <v>137.06</v>
+      </c>
+      <c r="H6" s="3">
+        <v>136.76</v>
+      </c>
+      <c r="I6" s="3">
+        <v>-0.2188822413541515</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>512</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>12990</v>
+      </c>
+      <c r="F7" s="2">
+        <v>13950</v>
+      </c>
+      <c r="G7" s="3">
+        <v>259.8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>279.0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7.390300230946882</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>1024</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>41365</v>
+      </c>
+      <c r="F8" s="2">
+        <v>37307</v>
+      </c>
+      <c r="G8" s="3">
+        <v>827.3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>746.14</v>
+      </c>
+      <c r="I8" s="3">
+        <v>-9.810226036504291</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>2048</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>65677</v>
+      </c>
+      <c r="F9" s="2">
+        <v>65677</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1313.54</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1313.54</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>128</v>
+      </c>
+      <c r="B10" s="2">
+        <v>64</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4233</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4233</v>
+      </c>
+      <c r="G10" s="3">
+        <v>84.66</v>
+      </c>
+      <c r="H10" s="3">
+        <v>84.66</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>512</v>
+      </c>
+      <c r="B11" s="2">
+        <v>64</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2">
+        <v>47658</v>
+      </c>
+      <c r="F11" s="2">
+        <v>51711</v>
+      </c>
+      <c r="G11" s="3">
+        <v>953.16</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1034.22</v>
+      </c>
+      <c r="I11" s="3">
+        <v>8.504343447060304</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>512</v>
+      </c>
+      <c r="B12" s="2">
+        <v>64</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2">
+        <v>47210</v>
+      </c>
+      <c r="F12" s="2">
+        <v>51258</v>
+      </c>
+      <c r="G12" s="3">
+        <v>944.2</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1025.16</v>
+      </c>
+      <c r="I12" s="3">
+        <v>8.574454564710866</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K12"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="30"/>
@@ -2464,9 +3067,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2681,36 +3284,58 @@
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Six unit cases; twenty MFCC configurations</t>
+          <t>Six unit cases; twenty MFCC configurations; supplied 50 MHz OOC result</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>Simulation passes; new physical resource/timing mapping pending</t>
+          <t>Local regression passes; latest hardware fields supplied in result summaries</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/README.md</t>
+          <t>matrix_register_50MHz_20261027/README.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>Standalone DCT comparison</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>64-point register MatrixDCT versus recursive SkewDCT; 50 MHz</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Included; resources, first/final latency and WNS/WHS; supplied summaries</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>dct/DCT_Standalone.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D10"/>
+  <autoFilter ref="A1:D11"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="65" customWidth="1"/>
   </cols>
@@ -2728,7 +3353,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Archive filename</t>
+          <t>Archive or summary filename</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -2738,7 +3363,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Archive SHA256</t>
+          <t>SHA256</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -2962,15 +3587,85 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_20261027_json</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Register MatrixDCT and recursive SkewDCT, 50 MHz</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>results.json</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>2413</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>193620521ac3fd20b196d5be97bd3ed02b220c8446d9844450d296192b4ed93c</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>0dce6b054028ff37c3158adc0184acc030211d0e</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_20261027_csv</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Register MatrixDCT and recursive SkewDCT, 50 MHz</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>results.csv</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>766</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>a98e913348e6c9c73f8827a10f9ad22a301423735e3c70e82f2e09a71315b348</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>0dce6b054028ff37c3158adc0184acc030211d0e</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="30"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -2997,156 +3692,180 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Current MatrixDCT uses register/LUT storage. Its new resource and timing fields are pending, not copied from the obsolete BRAM implementation. Latest verified N1024 batch: 43622 cycles. Original hardware reports remain historical evidence.</t>
+          <t>Register/LUT MatrixDCT hardware fields now use supplied 2026-10-27 50 MHz OOC post-route summaries. Original BRAM measurements remain historical. New whole-MFCC resources: 30110 LUT, 43473 FF, 6.5 BRAM, 19 DSP; batch 43622 cycles.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Selection rule</t>
+          <t>Standalone DCT scope</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Keep the latest valid value per test project and configuration. Architecture/pipeline/version names are not separate test projects.</t>
+          <t>Standalone top-level resources and latency are separate from the inclusive MFCC DCT hierarchy. Both standalone DCTs report zero BRAM; MatrixDCT uses one DSP and SkewDCT 41, so arithmetic parallelism remains different.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Configuration key</t>
+          <t>Supplied result evidence</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Project, backend under comparison, N, frequency, output lanes, frame count and stall condition identify a case. Inclusive hierarchy scope is retained.</t>
+          <t>CSV and JSON summaries agree; original Vivado reports and coefficient dumps were not supplied. Positive WNS/WHS are user-reported; TNS and setup/hold failure counts remain blank. No new whole-MFCC SkewDCT implementation results were supplied.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>Partial updates</t>
+          <t>Selection rule</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Refresh metrics separately: a 150 MHz resource update does not invent new 50/100 MHz resources. Unchanged metrics use the latest available reports. Runtime cycle counts use the latest matching regression and are converted by frequency.</t>
+          <t>Keep the latest valid value per test project and configuration. Architecture/pipeline/version names are not separate test projects.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>Sources</t>
+          <t>Configuration key</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Source paths in tables and JSON are relative to docs/benchmarks/. Per-metric source columns identify the original evidence; different metric groups can come from different packages.</t>
+          <t>Project, backend under comparison, N, frequency, output lanes, frame count and stall condition identify a case. Inclusive hierarchy scope is retained.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>Resource priority</t>
+          <t>Partial updates</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>LUT, FF, BRAM and DSP appear first. DCT/C64/SkewDCT8 hierarchy rows are already included in parent totals.</t>
+          <t>Refresh metrics separately: a 150 MHz resource update does not invent new 50/100 MHz resources. Unchanged metrics use the latest available reports. Runtime cycle counts use the latest matching regression and are converted by frequency.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>BRAM unit</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>One BRAM tile is a 36 Kb equivalent; each RAMB18 counts as 0.5 tile.</t>
+          <t>Source paths in tables and JSON are relative to docs/benchmarks/. Per-metric source columns identify the original evidence; different metric groups can come from different packages.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>FFT evidence</t>
+          <t>Resource priority</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>XFFT resource reports use fixed-size cores and a 10 ns synthesis clock; custom FFT resources use a shared runtime core after routing at 20 ns. The 64..2048 XFFT latency numbers use runtime_2048. These attributes remain source metadata, not version-specific result rows.</t>
+          <t>LUT, FF, BRAM and DSP appear first. DCT/C64/SkewDCT8 hierarchy rows are already included in parent totals.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>FFT 16-point counting</t>
+          <t>BRAM unit</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>Latest reported custom complete-frame latency is 82 cycles; its accompanying regression records 83. The primary table retains the latest reported value and marks this counting discrepancy.</t>
+          <t>One BRAM tile is a 36 Kb equivalent; each RAMB18 counts as 0.5 tile.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>FFT first output</t>
+          <t>FFT evidence</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>First-output cycles are taken from the latest package reporting that metric (2026-10-22); complete-frame comparisons are updated by the 2026-10-25 package.</t>
+          <t>XFFT resource reports use fixed-size cores and a 10 ns synthesis clock; custom FFT resources use a shared runtime core after routing at 20 ns. The 64..2048 XFFT latency numbers use runtime_2048. These attributes remain source metadata, not version-specific result rows.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>Timing/accuracy scope</t>
+          <t>FFT 16-point counting</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>Times are RTL cycles divided by MHz, not board/PS/DMA measurements. Four-frame averages are not independently measured single-frame latency or steady-state II. MFCC reference errors do not isolate DCT error or recognition accuracy.</t>
+          <t>Latest reported custom complete-frame latency is 82 cycles; its accompanying regression records 83. The primary table retains the latest reported value and marks this counting discrepancy.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>FFT first output</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>Superseded values remain in immutable original reports for traceability, outside primary tables. The explicit paired memory before/after experiment retains both required comparison sides.</t>
+          <t>First-output cycles are taken from the latest package reporting that metric (2026-10-22); complete-frame comparisons are updated by the 2026-10-25 package.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
+          <t>Timing/accuracy scope</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Times are RTL cycles divided by MHz, not board/PS/DMA measurements. Four-frame averages are not independently measured single-frame latency or steady-state II. MFCC reference errors do not isolate DCT error or recognition accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Superseded values remain in immutable original reports for traceability, outside primary tables. The explicit paired memory before/after experiment retains both required comparison sides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
           <t>200 MHz status</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>Not measured for the latest RTL. Frozen-route estimate is approximately -1.409 ns. The old 200 MHz run was interrupted during placement and is not a pass/fail result.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B16"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
 </file>
@@ -3366,7 +4085,7 @@
       </c>
       <c r="V2" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -3444,7 +4163,7 @@
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -3522,7 +4241,7 @@
       </c>
       <c r="V4" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -3547,54 +4266,42 @@
       <c r="F5" s="2">
         <v>50</v>
       </c>
-      <c r="G5" s="0" t="inlineStr">
+      <c r="G5" s="2">
+        <v>30110</v>
+      </c>
+      <c r="H5" s="2">
+        <v>43473</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J5" s="2">
+        <v>19</v>
+      </c>
+      <c r="K5" s="3">
+        <v>8.235</v>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H5" s="0" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="I5" s="0" t="inlineStr">
+      <c r="N5" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="J5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="P5" s="0" t="inlineStr">
         <is>
-          <t>PENDING_REGISTER_IMPLEMENTATION</t>
+          <t>PASS_REPORTED_WNS_WHS</t>
         </is>
       </c>
       <c r="Q5" s="2">
@@ -3608,17 +4315,17 @@
       </c>
       <c r="T5" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
       <c r="U5" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6743,7 @@
       </c>
       <c r="M2" s="0" t="inlineStr">
         <is>
-          <t>MEASURED</t>
+          <t>MEASURED_PREVIOUS_REPORT</t>
         </is>
       </c>
       <c r="N2" s="2">
@@ -6052,10 +6759,10 @@
         <v>3.4286065721184498</v>
       </c>
       <c r="R2" s="3">
-        <v>12.49161094141159</v>
+        <v>12.491610941411583</v>
       </c>
       <c r="S2" s="3">
-        <v>101.62445254003131</v>
+        <v>101.62445254003143</v>
       </c>
       <c r="T2" s="3">
         <v>16.04862513376996</v>
@@ -6072,7 +6779,7 @@
       </c>
       <c r="W2" s="0" t="inlineStr">
         <is>
-          <t>c64_pipeline_N1024_150MHz_20261026/results/rtl_precision_performance.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -6091,49 +6798,33 @@
       <c r="D3" s="2">
         <v>50</v>
       </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L3" s="0" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="E3" s="2">
+        <v>30110</v>
+      </c>
+      <c r="F3" s="2">
+        <v>43473</v>
+      </c>
+      <c r="G3" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1749</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2584</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
       </c>
       <c r="M3" s="0" t="inlineStr">
         <is>
-          <t>PENDING_REGISTER_IMPLEMENTATION</t>
+          <t>REPORTED_POST_ROUTE</t>
         </is>
       </c>
       <c r="N3" s="2">
@@ -6146,30 +6837,30 @@
         <v>872.44</v>
       </c>
       <c r="Q3" s="3">
-        <v>3.4285470932893625</v>
+        <v>3.428547093289361</v>
       </c>
       <c r="R3" s="3">
-        <v>12.490109975036425</v>
+        <v>12.490109975036418</v>
       </c>
       <c r="S3" s="3">
-        <v>101.60887915401372</v>
+        <v>101.60887915401383</v>
       </c>
       <c r="T3" s="3">
-        <v>16.04966887517948</v>
+        <v>16.049668875179485</v>
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
-          <t>matrix_register_20261026/verified_results.json</t>
+          <t>matrix_register_50MHz_20261027/results.json</t>
         </is>
       </c>
     </row>
@@ -6180,6 +6871,233 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultRowHeight="30"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DCT points</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>MHz</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>FF</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>BRAM tiles</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DSP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WNS ns</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>WHS ns</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>First output cycles</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Final output cycles</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>First output us</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Final output us</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Tested commit</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>MatrixDCT</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <v>64</v>
+      </c>
+      <c r="C2" s="2">
+        <v>50</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1847</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2717</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>12.74</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>PASS_REPORTED_WNS_WHS</t>
+        </is>
+      </c>
+      <c r="K2" s="2">
+        <v>4289</v>
+      </c>
+      <c r="L2" s="2">
+        <v>4352</v>
+      </c>
+      <c r="M2" s="3">
+        <v>85.78</v>
+      </c>
+      <c r="N2" s="3">
+        <v>87.04</v>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>0dce6b054028ff37c3158adc0184acc030211d0e</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>SkewDCT</t>
+        </is>
+      </c>
+      <c r="B3" s="2">
+        <v>64</v>
+      </c>
+      <c r="C3" s="2">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5113</v>
+      </c>
+      <c r="E3" s="2">
+        <v>12378</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>41</v>
+      </c>
+      <c r="H3" s="3">
+        <v>14.342</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>PASS_REPORTED_WNS_WHS</t>
+        </is>
+      </c>
+      <c r="K3" s="2">
+        <v>175</v>
+      </c>
+      <c r="L3" s="2">
+        <v>238</v>
+      </c>
+      <c r="M3" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="N3" s="3">
+        <v>4.76</v>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>0dce6b054028ff37c3158adc0184acc030211d0e</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="inlineStr">
+        <is>
+          <t>matrix_register_50MHz_20261027/results.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:P3"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="30"/>
@@ -6348,514 +7266,4 @@
   <autoFilter ref="A1:F6"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="30"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
-    <col min="11" max="11" width="65" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>FFT N</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Output lanes</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Stalls</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Frames</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Before cycles</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>After cycles</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Before batch us at 50MHz</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>After batch us at 50MHz</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Cycle change %</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Mismatches to own reference</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1226</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1226</v>
-      </c>
-      <c r="G2" s="3">
-        <v>24.52</v>
-      </c>
-      <c r="H2" s="3">
-        <v>24.52</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D3" s="2">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1393</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1407</v>
-      </c>
-      <c r="G3" s="3">
-        <v>27.86</v>
-      </c>
-      <c r="H3" s="3">
-        <v>28.14</v>
-      </c>
-      <c r="I3" s="3">
-        <v>1.0050251256281406</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>64</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2757</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2537</v>
-      </c>
-      <c r="G4" s="3">
-        <v>55.14</v>
-      </c>
-      <c r="H4" s="3">
-        <v>50.74</v>
-      </c>
-      <c r="I4" s="3">
-        <v>-7.979688066739208</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>128</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D5" s="2">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4304</v>
-      </c>
-      <c r="F5" s="2">
-        <v>4304</v>
-      </c>
-      <c r="G5" s="3">
-        <v>86.08</v>
-      </c>
-      <c r="H5" s="3">
-        <v>86.08</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>256</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D6" s="2">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2">
-        <v>6853</v>
-      </c>
-      <c r="F6" s="2">
-        <v>6838</v>
-      </c>
-      <c r="G6" s="3">
-        <v>137.06</v>
-      </c>
-      <c r="H6" s="3">
-        <v>136.76</v>
-      </c>
-      <c r="I6" s="3">
-        <v>-0.2188822413541515</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>512</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D7" s="2">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2">
-        <v>12990</v>
-      </c>
-      <c r="F7" s="2">
-        <v>13950</v>
-      </c>
-      <c r="G7" s="3">
-        <v>259.8</v>
-      </c>
-      <c r="H7" s="3">
-        <v>279.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>7.390300230946882</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>1024</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>41365</v>
-      </c>
-      <c r="F8" s="2">
-        <v>37307</v>
-      </c>
-      <c r="G8" s="3">
-        <v>827.3</v>
-      </c>
-      <c r="H8" s="3">
-        <v>746.14</v>
-      </c>
-      <c r="I8" s="3">
-        <v>-9.810226036504291</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>2048</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D9" s="2">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2">
-        <v>65677</v>
-      </c>
-      <c r="F9" s="2">
-        <v>65677</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1313.54</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1313.54</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>128</v>
-      </c>
-      <c r="B10" s="2">
-        <v>64</v>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D10" s="2">
-        <v>4</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4233</v>
-      </c>
-      <c r="F10" s="2">
-        <v>4233</v>
-      </c>
-      <c r="G10" s="3">
-        <v>84.66</v>
-      </c>
-      <c r="H10" s="3">
-        <v>84.66</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>512</v>
-      </c>
-      <c r="B11" s="2">
-        <v>64</v>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D11" s="2">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2">
-        <v>47658</v>
-      </c>
-      <c r="F11" s="2">
-        <v>51711</v>
-      </c>
-      <c r="G11" s="3">
-        <v>953.16</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1034.22</v>
-      </c>
-      <c r="I11" s="3">
-        <v>8.504343447060304</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>512</v>
-      </c>
-      <c r="B12" s="2">
-        <v>64</v>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D12" s="2">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2">
-        <v>47210</v>
-      </c>
-      <c r="F12" s="2">
-        <v>51258</v>
-      </c>
-      <c r="G12" s="3">
-        <v>944.2</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1025.16</v>
-      </c>
-      <c r="I12" s="3">
-        <v>8.574454564710866</v>
-      </c>
-      <c r="J12" s="2">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="inlineStr">
-        <is>
-          <t>evidence/baseline/raw_reports/mfcc_integration.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:K12"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-</worksheet>
 </file>